--- a/docs/dossiers/dossier-paris-11e-2c1acefd.xlsx
+++ b/docs/dossiers/dossier-paris-11e-2c1acefd.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 12/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 13/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-11e-2c1acefd.xlsx
+++ b/docs/dossiers/dossier-paris-11e-2c1acefd.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 13/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 14/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-11e-2c1acefd.xlsx
+++ b/docs/dossiers/dossier-paris-11e-2c1acefd.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 14/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 15/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-11e-2c1acefd.xlsx
+++ b/docs/dossiers/dossier-paris-11e-2c1acefd.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 15/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 16/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-11e-2c1acefd.xlsx
+++ b/docs/dossiers/dossier-paris-11e-2c1acefd.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 16/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 17/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-11e-2c1acefd.xlsx
+++ b/docs/dossiers/dossier-paris-11e-2c1acefd.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 17/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 18/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-11e-2c1acefd.xlsx
+++ b/docs/dossiers/dossier-paris-11e-2c1acefd.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 18/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 19/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-11e-2c1acefd.xlsx
+++ b/docs/dossiers/dossier-paris-11e-2c1acefd.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 19/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 20/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-11e-2c1acefd.xlsx
+++ b/docs/dossiers/dossier-paris-11e-2c1acefd.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 20/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 21/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
@@ -929,7 +929,7 @@
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 4,9 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +157 €/mois.</t>
+          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 3,9 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +341 €/mois.</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1082,7 @@
         </is>
       </c>
       <c r="B28" s="20" t="n">
-        <v>0.049</v>
+        <v>0.039</v>
       </c>
     </row>
     <row r="29">

--- a/docs/dossiers/dossier-paris-11e-2c1acefd.xlsx
+++ b/docs/dossiers/dossier-paris-11e-2c1acefd.xlsx
@@ -929,7 +929,7 @@
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 3,9 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +341 €/mois.</t>
+          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 4,9 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +157 €/mois.</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1082,7 @@
         </is>
       </c>
       <c r="B28" s="20" t="n">
-        <v>0.039</v>
+        <v>0.049</v>
       </c>
     </row>
     <row r="29">

--- a/docs/dossiers/dossier-paris-11e-2c1acefd.xlsx
+++ b/docs/dossiers/dossier-paris-11e-2c1acefd.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 21/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 22/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-11e-2c1acefd.xlsx
+++ b/docs/dossiers/dossier-paris-11e-2c1acefd.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 22/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 23/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-11e-2c1acefd.xlsx
+++ b/docs/dossiers/dossier-paris-11e-2c1acefd.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 23/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 24/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-11e-2c1acefd.xlsx
+++ b/docs/dossiers/dossier-paris-11e-2c1acefd.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 24/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 25/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-11e-2c1acefd.xlsx
+++ b/docs/dossiers/dossier-paris-11e-2c1acefd.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 25/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 26/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-11e-2c1acefd.xlsx
+++ b/docs/dossiers/dossier-paris-11e-2c1acefd.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 26/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 27/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-11e-2c1acefd.xlsx
+++ b/docs/dossiers/dossier-paris-11e-2c1acefd.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 27/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 28/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-11e-2c1acefd.xlsx
+++ b/docs/dossiers/dossier-paris-11e-2c1acefd.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 28/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 29/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-11e-2c1acefd.xlsx
+++ b/docs/dossiers/dossier-paris-11e-2c1acefd.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 29/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 30/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-11e-2c1acefd.xlsx
+++ b/docs/dossiers/dossier-paris-11e-2c1acefd.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 30/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 01/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-11e-2c1acefd.xlsx
+++ b/docs/dossiers/dossier-paris-11e-2c1acefd.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 01/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 02/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-11e-2c1acefd.xlsx
+++ b/docs/dossiers/dossier-paris-11e-2c1acefd.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 02/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 03/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-11e-2c1acefd.xlsx
+++ b/docs/dossiers/dossier-paris-11e-2c1acefd.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 03/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 04/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-11e-2c1acefd.xlsx
+++ b/docs/dossiers/dossier-paris-11e-2c1acefd.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 04/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 05/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-11e-2c1acefd.xlsx
+++ b/docs/dossiers/dossier-paris-11e-2c1acefd.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 05/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 06/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-11e-2c1acefd.xlsx
+++ b/docs/dossiers/dossier-paris-11e-2c1acefd.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 06/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 07/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-11e-2c1acefd.xlsx
+++ b/docs/dossiers/dossier-paris-11e-2c1acefd.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 07/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 08/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-11e-2c1acefd.xlsx
+++ b/docs/dossiers/dossier-paris-11e-2c1acefd.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 08/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 09/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-11e-2c1acefd.xlsx
+++ b/docs/dossiers/dossier-paris-11e-2c1acefd.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 09/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 10/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-11e-2c1acefd.xlsx
+++ b/docs/dossiers/dossier-paris-11e-2c1acefd.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 10/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 11/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-11e-2c1acefd.xlsx
+++ b/docs/dossiers/dossier-paris-11e-2c1acefd.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 11/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 12/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-11e-2c1acefd.xlsx
+++ b/docs/dossiers/dossier-paris-11e-2c1acefd.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 12/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 13/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
@@ -929,7 +929,7 @@
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 4,9 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +157 €/mois.</t>
+          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 5,34 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +73 €/mois.</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1082,7 @@
         </is>
       </c>
       <c r="B28" s="20" t="n">
-        <v>0.049</v>
+        <v>0.0534</v>
       </c>
     </row>
     <row r="29">

--- a/docs/dossiers/dossier-paris-11e-2c1acefd.xlsx
+++ b/docs/dossiers/dossier-paris-11e-2c1acefd.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 13/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 14/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-11e-2c1acefd.xlsx
+++ b/docs/dossiers/dossier-paris-11e-2c1acefd.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 14/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 15/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-11e-2c1acefd.xlsx
+++ b/docs/dossiers/dossier-paris-11e-2c1acefd.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 15/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 16/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-11e-2c1acefd.xlsx
+++ b/docs/dossiers/dossier-paris-11e-2c1acefd.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 16/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 17/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-11e-2c1acefd.xlsx
+++ b/docs/dossiers/dossier-paris-11e-2c1acefd.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 17/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 18/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-11e-2c1acefd.xlsx
+++ b/docs/dossiers/dossier-paris-11e-2c1acefd.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 18/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 19/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-11e-2c1acefd.xlsx
+++ b/docs/dossiers/dossier-paris-11e-2c1acefd.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 19/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 20/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-11e-2c1acefd.xlsx
+++ b/docs/dossiers/dossier-paris-11e-2c1acefd.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 20/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 21/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-11e-2c1acefd.xlsx
+++ b/docs/dossiers/dossier-paris-11e-2c1acefd.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 21/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 22/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-11e-2c1acefd.xlsx
+++ b/docs/dossiers/dossier-paris-11e-2c1acefd.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 22/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 23/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-11e-2c1acefd.xlsx
+++ b/docs/dossiers/dossier-paris-11e-2c1acefd.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Annonce" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Synthèse'!$A$1:$C$58</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Synthèse'!$A$1:$C$59</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -793,7 +793,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F57"/>
+  <dimension ref="A1:F58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -860,7 +860,7 @@
         </is>
       </c>
       <c r="B8" s="10">
-        <f>B25</f>
+        <f>B26</f>
         <v/>
       </c>
       <c r="E8" s="6" t="inlineStr">
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="F8" s="8">
-        <f>B38-(B43+B44+B45)/12</f>
+        <f>B39-(B44+B45+B46)/12</f>
         <v/>
       </c>
     </row>
@@ -880,7 +880,7 @@
         </is>
       </c>
       <c r="B9" s="10">
-        <f>B36</f>
+        <f>B37</f>
         <v/>
       </c>
       <c r="E9" s="6" t="inlineStr">
@@ -889,7 +889,7 @@
         </is>
       </c>
       <c r="F9" s="8">
-        <f>B49</f>
+        <f>B50</f>
         <v/>
       </c>
     </row>
@@ -900,7 +900,7 @@
         </is>
       </c>
       <c r="B10" s="11">
-        <f>B38</f>
+        <f>B39</f>
         <v/>
       </c>
     </row>
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="B11" s="11">
-        <f>B49</f>
+        <f>B50</f>
         <v/>
       </c>
     </row>
@@ -922,14 +922,14 @@
         </is>
       </c>
       <c r="B12" s="12">
-        <f>B54</f>
+        <f>B55</f>
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 5,34 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +73 €/mois.</t>
+          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 5,34 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +132 €/mois.</t>
         </is>
       </c>
     </row>
@@ -970,7 +970,7 @@
         </is>
       </c>
       <c r="B18" s="17" t="n">
-        <v>397000</v>
+        <v>387000</v>
       </c>
     </row>
     <row r="19">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="C21" s="18" t="inlineStr">
         <is>
-          <t>ce bien est 38 % au-dessus de la médiane locale</t>
+          <t>ce bien est 34 % au-dessus de la médiane locale</t>
         </is>
       </c>
     </row>
@@ -1033,364 +1033,381 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="7" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="14" t="inlineStr">
+        <is>
+          <t>Évolution du prix demandé</t>
+        </is>
+      </c>
+      <c r="B23" s="15" t="inlineStr">
+        <is>
+          <t>397 000 € (08/09) → 387 000 € (23/10)  —  −2.5 % depuis la première vue</t>
+        </is>
+      </c>
+      <c r="C23" s="18" t="inlineStr">
+        <is>
+          <t>un prix qui baisse est un levier de négociation documenté</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="7" t="inlineStr">
         <is>
           <t>HYPOTHÈSES — cellules jaunes à ajuster avec votre conseiller</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="14" t="inlineStr">
-        <is>
-          <t>Prix négocié retenu</t>
-        </is>
-      </c>
-      <c r="B25" s="19" t="n">
-        <v>397000</v>
-      </c>
-      <c r="C25" s="18" t="inlineStr">
-        <is>
-          <t>par défaut le prix affiché — un prix demandé se négocie</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="14" t="inlineStr">
         <is>
-          <t>Frais d'acquisition (notaire, garanties)</t>
-        </is>
-      </c>
-      <c r="B26" s="20" t="n">
-        <v>0.08</v>
+          <t>Prix négocié retenu</t>
+        </is>
+      </c>
+      <c r="B26" s="19" t="n">
+        <v>387000</v>
+      </c>
+      <c r="C26" s="18" t="inlineStr">
+        <is>
+          <t>par défaut le prix affiché — un prix demandé se négocie</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="14" t="inlineStr">
         <is>
-          <t>Apport personnel</t>
+          <t>Frais d'acquisition (notaire, garanties)</t>
         </is>
       </c>
       <c r="B27" s="20" t="n">
-        <v>0.2</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="14" t="inlineStr">
         <is>
-          <t>Taux du crédit (hors assurance)</t>
+          <t>Apport personnel</t>
         </is>
       </c>
       <c r="B28" s="20" t="n">
-        <v>0.0534</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="14" t="inlineStr">
         <is>
-          <t>Durée du crédit (années)</t>
-        </is>
-      </c>
-      <c r="B29" s="21" t="n">
-        <v>20</v>
+          <t>Taux du crédit (hors assurance)</t>
+        </is>
+      </c>
+      <c r="B29" s="20" t="n">
+        <v>0.0534</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="14" t="inlineStr">
         <is>
-          <t>Taxe foncière (en mois de loyer par an)</t>
-        </is>
-      </c>
-      <c r="B30" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="C30" s="18" t="inlineStr">
-        <is>
-          <t>à remplacer par le montant réel dès que connu</t>
-        </is>
+          <t>Durée du crédit (années)</t>
+        </is>
+      </c>
+      <c r="B30" s="21" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="14" t="inlineStr">
         <is>
-          <t>Provision entretien &amp; vacance (% du loyer)</t>
-        </is>
-      </c>
-      <c r="B31" s="20" t="n">
-        <v>0.05</v>
+          <t>Taxe foncière (en mois de loyer par an)</t>
+        </is>
+      </c>
+      <c r="B31" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C31" s="18" t="inlineStr">
+        <is>
+          <t>à remplacer par le montant réel dès que connu</t>
+        </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="14" t="inlineStr">
         <is>
+          <t>Provision entretien &amp; vacance (% du loyer)</t>
+        </is>
+      </c>
+      <c r="B32" s="20" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="14" t="inlineStr">
+        <is>
           <t>Assurance propriétaire (PNO, €/an)</t>
         </is>
       </c>
-      <c r="B32" s="19" t="n">
+      <c r="B33" s="19" t="n">
         <v>300</v>
       </c>
     </row>
-    <row r="34" ht="18" customHeight="1">
-      <c r="A34" s="7" t="inlineStr">
+    <row r="35" ht="18" customHeight="1">
+      <c r="A35" s="7" t="inlineStr">
         <is>
           <t>PLAN DE FINANCEMENT</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="14" t="inlineStr">
-        <is>
-          <t>Coût d'acquisition total</t>
-        </is>
-      </c>
-      <c r="B35" s="17">
-        <f>B25*(1+B26)</f>
-        <v/>
-      </c>
-      <c r="C35" s="18" t="inlineStr">
-        <is>
-          <t>prix négocié + frais d'acquisition</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="14" t="inlineStr">
         <is>
-          <t>Apport personnel</t>
+          <t>Coût d'acquisition total</t>
         </is>
       </c>
       <c r="B36" s="17">
-        <f>B35*B27</f>
-        <v/>
+        <f>B26*(1+B27)</f>
+        <v/>
+      </c>
+      <c r="C36" s="18" t="inlineStr">
+        <is>
+          <t>prix négocié + frais d'acquisition</t>
+        </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="14" t="inlineStr">
         <is>
-          <t>Montant emprunté</t>
+          <t>Apport personnel</t>
         </is>
       </c>
       <c r="B37" s="17">
-        <f>B35-B36</f>
+        <f>B36*B28</f>
         <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="14" t="inlineStr">
         <is>
-          <t>Mensualité du crédit</t>
-        </is>
-      </c>
-      <c r="B38" s="23">
-        <f>IFERROR(-PMT(B28/12,B29*12,B37),0)</f>
+          <t>Montant emprunté</t>
+        </is>
+      </c>
+      <c r="B38" s="17">
+        <f>B36-B37</f>
         <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="14" t="inlineStr">
         <is>
+          <t>Mensualité du crédit</t>
+        </is>
+      </c>
+      <c r="B39" s="23">
+        <f>IFERROR(-PMT(B29/12,B30*12,B38),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="14" t="inlineStr">
+        <is>
           <t>Service de la dette (annuel)</t>
         </is>
       </c>
-      <c r="B39" s="17">
-        <f>B38*12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41" ht="18" customHeight="1">
-      <c r="A41" s="7" t="inlineStr">
+      <c r="B40" s="17">
+        <f>B39*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="A42" s="7" t="inlineStr">
         <is>
           <t>EXPLOITATION ANNUELLE</t>
         </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="14" t="inlineStr">
-        <is>
-          <t>Loyers annuels HT</t>
-        </is>
-      </c>
-      <c r="B42" s="17">
-        <f>IFERROR(B20*12,0)</f>
-        <v/>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="14" t="inlineStr">
         <is>
-          <t>− Taxe foncière</t>
+          <t>Loyers annuels HT</t>
         </is>
       </c>
       <c r="B43" s="17">
-        <f>-IFERROR(B20*B30,0)</f>
+        <f>IFERROR(B20*12,0)</f>
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="14" t="inlineStr">
         <is>
-          <t>− Entretien &amp; vacance locative</t>
+          <t>− Taxe foncière</t>
         </is>
       </c>
       <c r="B44" s="17">
-        <f>-B42*B31</f>
+        <f>-IFERROR(B20*B31,0)</f>
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="14" t="inlineStr">
         <is>
-          <t>− Assurance PNO</t>
+          <t>− Entretien &amp; vacance locative</t>
         </is>
       </c>
       <c r="B45" s="17">
-        <f>-B32</f>
+        <f>-B43*B32</f>
         <v/>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="14" t="inlineStr">
         <is>
-          <t>Revenu net avant crédit</t>
+          <t>− Assurance PNO</t>
         </is>
       </c>
       <c r="B46" s="17">
-        <f>B42+B43+B44+B45</f>
+        <f>-B33</f>
         <v/>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="14" t="inlineStr">
         <is>
-          <t>− Remboursement du crédit</t>
+          <t>Revenu net avant crédit</t>
         </is>
       </c>
       <c r="B47" s="17">
-        <f>-B39</f>
+        <f>B43+B44+B45+B46</f>
         <v/>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="14" t="inlineStr">
         <is>
-          <t>Cash-flow annuel</t>
+          <t>− Remboursement du crédit</t>
         </is>
       </c>
       <c r="B48" s="17">
-        <f>B46-B39</f>
+        <f>-B40</f>
         <v/>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="14" t="inlineStr">
         <is>
+          <t>Cash-flow annuel</t>
+        </is>
+      </c>
+      <c r="B49" s="17">
+        <f>B47-B40</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="14" t="inlineStr">
+        <is>
           <t>Cash-flow mensuel</t>
         </is>
       </c>
-      <c r="B49" s="24">
-        <f>B48/12</f>
-        <v/>
-      </c>
-      <c r="C49" s="18" t="inlineStr">
+      <c r="B50" s="24">
+        <f>B49/12</f>
+        <v/>
+      </c>
+      <c r="C50" s="18" t="inlineStr">
         <is>
           <t>positif : le bien se paie tout seul, loyer ≥ crédit + charges</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="18" customHeight="1">
-      <c r="A51" s="7" t="inlineStr">
+    <row r="52" ht="18" customHeight="1">
+      <c r="A52" s="7" t="inlineStr">
         <is>
           <t>LES RATIOS QUE REGARDE LE BANQUIER</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="14" t="inlineStr">
-        <is>
-          <t>Rendement brut</t>
-        </is>
-      </c>
-      <c r="B52" s="25">
-        <f>IFERROR(B42/B25,"")</f>
-        <v/>
-      </c>
-      <c r="C52" s="18" t="inlineStr">
-        <is>
-          <t>loyer annuel ÷ prix — la base de comparaison des biens</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="14" t="inlineStr">
         <is>
-          <t>Rendement net avant crédit</t>
+          <t>Rendement brut</t>
         </is>
       </c>
       <c r="B53" s="25">
-        <f>IFERROR(B46/B35,"")</f>
+        <f>IFERROR(B43/B26,"")</f>
         <v/>
       </c>
       <c r="C53" s="18" t="inlineStr">
         <is>
-          <t>après taxe foncière, entretien et assurance</t>
+          <t>loyer annuel ÷ prix — la base de comparaison des biens</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="14" t="inlineStr">
         <is>
-          <t>DSCR — couverture de la dette</t>
-        </is>
-      </c>
-      <c r="B54" s="26">
-        <f>IFERROR(B46/B39,"")</f>
+          <t>Rendement net avant crédit</t>
+        </is>
+      </c>
+      <c r="B54" s="25">
+        <f>IFERROR(B47/B36,"")</f>
         <v/>
       </c>
       <c r="C54" s="18" t="inlineStr">
         <is>
-          <t>revenu net ÷ crédit : ≥ 1,20 rassure une banque</t>
+          <t>après taxe foncière, entretien et assurance</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="14" t="inlineStr">
         <is>
-          <t>LTV — part financée par la banque</t>
-        </is>
-      </c>
-      <c r="B55" s="25">
-        <f>IFERROR(B37/B25,"")</f>
+          <t>DSCR — couverture de la dette</t>
+        </is>
+      </c>
+      <c r="B55" s="26">
+        <f>IFERROR(B47/B40,"")</f>
         <v/>
       </c>
       <c r="C55" s="18" t="inlineStr">
         <is>
-          <t>≤ 80 % est la zone de confort bancaire</t>
+          <t>revenu net ÷ crédit : ≥ 1,20 rassure une banque</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="14" t="inlineStr">
         <is>
-          <t>Effort d'épargne mensuel si négatif</t>
-        </is>
-      </c>
-      <c r="B56" s="23">
-        <f>MAX(0,-B48/12)</f>
-        <v/>
+          <t>LTV — part financée par la banque</t>
+        </is>
+      </c>
+      <c r="B56" s="25">
+        <f>IFERROR(B38/B26,"")</f>
+        <v/>
+      </c>
+      <c r="C56" s="18" t="inlineStr">
+        <is>
+          <t>≤ 80 % est la zone de confort bancaire</t>
+        </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="14" t="inlineStr">
         <is>
+          <t>Effort d'épargne mensuel si négatif</t>
+        </is>
+      </c>
+      <c r="B57" s="23">
+        <f>MAX(0,-B49/12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="14" t="inlineStr">
+        <is>
           <t>Score de l'outil de veille</t>
         </is>
       </c>
-      <c r="B57" s="15" t="inlineStr">
+      <c r="B58" s="15" t="inlineStr">
         <is>
           <t>70/100</t>
         </is>
       </c>
-      <c r="C57" s="18" t="inlineStr">
+      <c r="C58" s="18" t="inlineStr">
         <is>
           <t>rendement, emplacement, prix vs marché, financement, fiscalité</t>
         </is>
@@ -1399,18 +1416,18 @@
   </sheetData>
   <mergeCells count="11">
     <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A41:C41"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="A42:C42"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A3:C3"/>
     <mergeCell ref="A13:C14"/>
-    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="A35:C35"/>
     <mergeCell ref="A15:C15"/>
     <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A24:C24"/>
     <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A51:C51"/>
+    <mergeCell ref="A52:C52"/>
   </mergeCells>
-  <conditionalFormatting sqref="B48">
+  <conditionalFormatting sqref="B49">
     <cfRule type="cellIs" priority="1" operator="greaterThanOrEqual" dxfId="0">
       <formula>0</formula>
     </cfRule>
@@ -1418,7 +1435,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B49">
+  <conditionalFormatting sqref="B50">
     <cfRule type="cellIs" priority="3" operator="greaterThanOrEqual" dxfId="0">
       <formula>0</formula>
     </cfRule>
@@ -1426,7 +1443,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B54">
+  <conditionalFormatting sqref="B55">
     <cfRule type="cellIs" priority="5" operator="greaterThanOrEqual" dxfId="0">
       <formula>1.2</formula>
     </cfRule>
@@ -1503,7 +1520,7 @@
         </is>
       </c>
       <c r="G1">
-        <f>'Synthèse'!B29</f>
+        <f>'Synthèse'!B30</f>
         <v/>
       </c>
     </row>
@@ -1512,7 +1529,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="8">
-        <f>IF(A2&lt;=$G$1,'Synthèse'!$B$37,"")</f>
+        <f>IF(A2&lt;=$G$1,'Synthèse'!$B$38,"")</f>
         <v/>
       </c>
       <c r="C2" s="8">
@@ -1533,7 +1550,7 @@
         </is>
       </c>
       <c r="G2">
-        <f>'Synthèse'!B28</f>
+        <f>'Synthèse'!B29</f>
         <v/>
       </c>
     </row>
@@ -1558,7 +1575,7 @@
         <v/>
       </c>
       <c r="G3">
-        <f>'Synthèse'!B39</f>
+        <f>'Synthèse'!B40</f>
         <v/>
       </c>
     </row>
@@ -2261,7 +2278,7 @@
       </c>
       <c r="B8" s="29" t="inlineStr">
         <is>
-          <t>stable depuis la première vue</t>
+          <t>397 000 € (08/09) → 387 000 € (23/10)  —  −2.5 % depuis la première vue</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-11e-2c1acefd.xlsx
+++ b/docs/dossiers/dossier-paris-11e-2c1acefd.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 23/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 24/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-11e-2c1acefd.xlsx
+++ b/docs/dossiers/dossier-paris-11e-2c1acefd.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 24/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 25/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-11e-2c1acefd.xlsx
+++ b/docs/dossiers/dossier-paris-11e-2c1acefd.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 25/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 26/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
@@ -2314,7 +2314,7 @@
       </c>
       <c r="B11" s="29" t="inlineStr">
         <is>
-          <t>loyer_estime</t>
+          <t>loyer_estime · occupation_a_confirmer</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-11e-2c1acefd.xlsx
+++ b/docs/dossiers/dossier-paris-11e-2c1acefd.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 26/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 27/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
@@ -1404,7 +1404,7 @@
       </c>
       <c r="B58" s="15" t="inlineStr">
         <is>
-          <t>70/100</t>
+          <t>68/100</t>
         </is>
       </c>
       <c r="C58" s="18" t="inlineStr">

--- a/docs/dossiers/dossier-paris-11e-2c1acefd.xlsx
+++ b/docs/dossiers/dossier-paris-11e-2c1acefd.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 27/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 28/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-11e-2c1acefd.xlsx
+++ b/docs/dossiers/dossier-paris-11e-2c1acefd.xlsx
@@ -2326,7 +2326,7 @@
       </c>
       <c r="B12" s="29" t="inlineStr">
         <is>
-          <t>Vente de murs de boutique libres – Rue Sedaine, Paris 11ᵉ Idéalement située rue Sedaine, dans un secteur dynamique en plein essor bénéficiant de l'implantation de nombreux commerces variés et de qualité, cette belle boutique libre d'occupation développe une superficie de 42 m² de plain-pied. Elle bénéficie d'une vitrine de 4 mètres linéaires, offrant une excellente visibilité. En parfait état général, le local comprend une pièce sur rue avec point d'eau, une pièce en arrière-boutique disposant d'une fenêtre et d'un accès direct sur cour, un WC et un couloir de distribution. Atout majeur : l'absence de murs porteurs permet de repenser entièrement l'agencement et d'ouvrir les espaces selon vos besoins. Ce bien conviendra aussi bien à un exploitant qu'à un investisseur, avec une valeur locative estimée à 24 000 € HT HC par an. Tous les commerces sont envisageables, à l'exception des activités de restauration nécessitant un conduit d'extraction, le local n'en étant pas équipé. Prix de vente : 397 000 € FAI Réf. Agence : VEMU 1027</t>
+          <t>Vente de murs de boutique libres – Rue Sedaine, Paris 11ᵉ Idéalement située rue Sedaine, dans un secteur dynamique en plein essor bénéficiant de l'implantation de nombreux commerces variés et de qualité, cette belle boutique libre d'occupation développe une superficie de 42 m² de plain-pied. Elle bénéficie d'une vitrine de 4 mètres linéaires, offrant une excellente visibilité. En parfait état général, le local comprend une pièce sur rue avec point d'eau, une pièce en arrière-boutique disposant d'une fenêtre et d'un accès direct sur cour, un WC et un couloir de distribution. Atout majeur : l'absence de murs porteurs permet de repenser entièrement l'agencement et d'ouvrir les espaces selon vos besoins. Ce bien conviendra aussi bien à un exploitant qu'à un investisseur, avec une valeur locative estimée à 24 000 € HT HC par an. Tous les commerces sont envisageables, à l'exception des activités de restauration nécessitant un conduit d'extraction, le local n'en étant pas équipé. Prix de vente : 387 000 € FAI Réf. Agence : VEMU 1027</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-11e-2c1acefd.xlsx
+++ b/docs/dossiers/dossier-paris-11e-2c1acefd.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 28/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 29/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-11e-2c1acefd.xlsx
+++ b/docs/dossiers/dossier-paris-11e-2c1acefd.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 29/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 30/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-11e-2c1acefd.xlsx
+++ b/docs/dossiers/dossier-paris-11e-2c1acefd.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 30/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 31/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
